--- a/backend/Rwanda/technoeconomic-inputs-Aligned.xlsx
+++ b/backend/Rwanda/technoeconomic-inputs-Aligned.xlsx
@@ -3,12 +3,11 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Electricity" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="LPG" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Ethanol" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterate="1"/>
@@ -17,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+  </numFmts>
   <fonts count="7">
     <font>
       <name val="Calibri"/>
@@ -135,7 +136,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -175,6 +176,18 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -523,7 +536,8 @@
   <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col width="44.36328125" customWidth="1" min="1" max="1"/>
+    <col width="26.1796875" customWidth="1" min="1" max="1"/>
+    <col width="19.26953125" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.5" customHeight="1">
@@ -595,41 +609,41 @@
           <t>$/kWh</t>
         </is>
       </c>
-      <c r="D2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" s="8" t="n">
-        <v>0</v>
+      <c r="D2" s="14" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E2" s="14" t="n">
+        <v>0.1575</v>
+      </c>
+      <c r="F2" s="14" t="n">
+        <v>0.165375</v>
+      </c>
+      <c r="G2" s="14" t="n">
+        <v>0.17364375</v>
+      </c>
+      <c r="H2" s="14" t="n">
+        <v>0.1823259375000001</v>
+      </c>
+      <c r="I2" s="14" t="n">
+        <v>0.1914422343750001</v>
+      </c>
+      <c r="J2" s="14" t="n">
+        <v>0.2010143460937501</v>
+      </c>
+      <c r="K2" s="14" t="n">
+        <v>0.2110650633984376</v>
+      </c>
+      <c r="L2" s="14" t="n">
+        <v>0.2216183165683595</v>
+      </c>
+      <c r="M2" s="14" t="n">
+        <v>0.2326992323967775</v>
+      </c>
+      <c r="N2" s="14" t="n">
+        <v>0.2443341940166164</v>
+      </c>
+      <c r="O2" s="14" t="n">
+        <v>0.2565509037174472</v>
       </c>
     </row>
     <row r="3" ht="15.5" customHeight="1">
@@ -649,40 +663,40 @@
         </is>
       </c>
       <c r="D3" s="8" t="n">
-        <v>0</v>
+        <v>1810.540773471098</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>0</v>
+        <v>1976.489613521989</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>0</v>
+        <v>2098.254169723408</v>
       </c>
       <c r="G3" s="8" t="n">
-        <v>0</v>
+        <v>2208.45211518827</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>0</v>
+        <v>2307.694987877016</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>0</v>
+        <v>2396.572443165438</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>0</v>
+        <v>2504.958896468817</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>0</v>
+        <v>2640.857234534843</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>0</v>
+        <v>2397.745266650606</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>0</v>
+        <v>2499.075390512704</v>
       </c>
       <c r="N3" s="8" t="n">
-        <v>0</v>
+        <v>2589.37486642809</v>
       </c>
       <c r="O3" s="8" t="n">
-        <v>0</v>
+        <v>2669.271272861673</v>
       </c>
     </row>
     <row r="4" ht="15.5" customHeight="1">
@@ -779,40 +793,40 @@
         </is>
       </c>
       <c r="D5" s="8" t="n">
-        <v>0</v>
+        <v>242.2034336438869</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>0</v>
+        <v>294.738372505465</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>0</v>
+        <v>291.7909887804103</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>0</v>
+        <v>288.8730788926063</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>0</v>
+        <v>285.9843481036802</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0</v>
+        <v>283.1245046226434</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>0</v>
+        <v>340.6604887506167</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>0</v>
+        <v>397.3185185043754</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>0</v>
+        <v>393.3453333193316</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>0</v>
+        <v>389.4118799861384</v>
       </c>
       <c r="N5" s="8" t="n">
-        <v>0</v>
+        <v>385.517761186277</v>
       </c>
       <c r="O5" s="8" t="n">
-        <v>0</v>
+        <v>259.2152122039375</v>
       </c>
     </row>
     <row r="6" ht="15.5" customHeight="1">
@@ -885,40 +899,40 @@
         </is>
       </c>
       <c r="D7" s="8" t="n">
-        <v>0</v>
+        <v>48.20089562467992</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>0</v>
+        <v>53.30695790850994</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>0</v>
+        <v>59.61987738863688</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>0</v>
+        <v>65.80120778337044</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>0</v>
+        <v>71.85294958247047</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0</v>
+        <v>77.77707642481016</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>0</v>
+        <v>83.5755354353448</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>0</v>
+        <v>92.57276382194368</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>0</v>
+        <v>101.4170548475285</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>0</v>
+        <v>110.0752027762195</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>0</v>
+        <v>118.5500460408519</v>
       </c>
       <c r="O7" s="8" t="n">
-        <v>0</v>
+        <v>126.844384919914</v>
       </c>
     </row>
     <row r="8" ht="15.5" customHeight="1">
@@ -938,7 +952,7 @@
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="E8" s="10" t="n">
         <v>0</v>
@@ -990,41 +1004,41 @@
           <t>$/kWh</t>
         </is>
       </c>
-      <c r="D9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="8" t="n">
-        <v>0</v>
+      <c r="D9" s="14" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>0.1575</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>0.165375</v>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>0.17364375</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>0.1823259375000001</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>0.1914422343750001</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>0.2010143460937501</v>
+      </c>
+      <c r="K9" s="14" t="n">
+        <v>0.2110650633984376</v>
+      </c>
+      <c r="L9" s="14" t="n">
+        <v>0.2216183165683595</v>
+      </c>
+      <c r="M9" s="14" t="n">
+        <v>0.2326992323967775</v>
+      </c>
+      <c r="N9" s="14" t="n">
+        <v>0.2443341940166164</v>
+      </c>
+      <c r="O9" s="14" t="n">
+        <v>0.2565509037174472</v>
       </c>
     </row>
     <row r="10" ht="15.5" customHeight="1">
@@ -1044,40 +1058,40 @@
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>0</v>
+        <v>452.6351933677747</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>0</v>
+        <v>463.6210204557751</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0</v>
+        <v>460.5923787197725</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>0</v>
+        <v>452.3335657614529</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>0</v>
+        <v>439.5609500718126</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>0</v>
+        <v>422.9245487939008</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>0</v>
+        <v>407.7840064019006</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>0</v>
+        <v>394.6108511373904</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>0</v>
+        <v>326.9652636341735</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>0</v>
+        <v>308.8744864678623</v>
       </c>
       <c r="N10" s="8" t="n">
-        <v>0</v>
+        <v>287.7083184920099</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>0</v>
+        <v>263.9938621511545</v>
       </c>
     </row>
     <row r="11" ht="15.5" customHeight="1">
@@ -1174,40 +1188,40 @@
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>0</v>
+        <v>39.20533020612309</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>0</v>
+        <v>49.66803257508351</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0</v>
+        <v>49.17135224933267</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>0</v>
+        <v>48.67963872683934</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>0</v>
+        <v>48.19284233957096</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0</v>
+        <v>47.71091391617525</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>0</v>
+        <v>17.3764528627935</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>0</v>
+        <v>-12.50500172575464</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>0</v>
+        <v>-12.37995170849709</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>0</v>
+        <v>-12.25615219141212</v>
       </c>
       <c r="N12" s="8" t="n">
-        <v>0</v>
+        <v>-12.133590669498</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>0</v>
+        <v>0.9231042276977806</v>
       </c>
     </row>
     <row r="13" ht="15.5" customHeight="1">
@@ -1280,40 +1294,40 @@
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>0</v>
+        <v>56.13416700255231</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>0</v>
+        <v>63.13219928987156</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0</v>
+        <v>71.77450880827612</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>0</v>
+        <v>80.23765891638362</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>0</v>
+        <v>88.52436857144815</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>0</v>
+        <v>96.63732026751975</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>0</v>
+        <v>104.5791604928127</v>
       </c>
       <c r="K14" s="8" t="n">
-        <v>0</v>
+        <v>103.3411052008041</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>0</v>
+        <v>98.26081872793341</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>0</v>
+        <v>93.27180387400006</v>
       </c>
       <c r="N14" s="8" t="n">
-        <v>0</v>
+        <v>88.37274323527257</v>
       </c>
       <c r="O14" s="8" t="n">
-        <v>0</v>
+        <v>83.56233662893223</v>
       </c>
     </row>
     <row r="15" ht="15.5" customHeight="1">
@@ -1333,7 +1347,7 @@
         </is>
       </c>
       <c r="D15" s="10" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E15" s="10" t="n">
         <v>0</v>
@@ -1445,41 +1459,41 @@
           <t>$/kWh</t>
         </is>
       </c>
-      <c r="C2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" s="8" t="n">
-        <v>0</v>
+      <c r="C2" s="16" t="n">
+        <v>0.076103500761035</v>
+      </c>
+      <c r="D2" s="16" t="n">
+        <v>0.07990867579908675</v>
+      </c>
+      <c r="E2" s="16" t="n">
+        <v>0.0839041095890411</v>
+      </c>
+      <c r="F2" s="16" t="n">
+        <v>0.08809931506849315</v>
+      </c>
+      <c r="G2" s="16" t="n">
+        <v>0.09250428082191782</v>
+      </c>
+      <c r="H2" s="16" t="n">
+        <v>0.09712949486301371</v>
+      </c>
+      <c r="I2" s="16" t="n">
+        <v>0.1019859696061644</v>
+      </c>
+      <c r="J2" s="16" t="n">
+        <v>0.1070852680864726</v>
+      </c>
+      <c r="K2" s="16" t="n">
+        <v>0.1124395314907963</v>
+      </c>
+      <c r="L2" s="16" t="n">
+        <v>0.1180615080653361</v>
+      </c>
+      <c r="M2" s="16" t="n">
+        <v>0.1239645834686029</v>
+      </c>
+      <c r="N2" s="16" t="n">
+        <v>0.1301628126420331</v>
       </c>
     </row>
     <row r="3" ht="15.5" customHeight="1">
@@ -1494,40 +1508,40 @@
         </is>
       </c>
       <c r="C3" s="8" t="n">
-        <v>0</v>
+        <v>72.4648857632267</v>
       </c>
       <c r="D3" s="8" t="n">
-        <v>0</v>
+        <v>108.5536134229659</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>0</v>
+        <v>149.9878561799062</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>0</v>
+        <v>183.2242850996296</v>
       </c>
       <c r="G3" s="8" t="n">
-        <v>0</v>
+        <v>206.5424331604688</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>0</v>
+        <v>222.1876901878082</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>0</v>
+        <v>231.0777721112869</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>0</v>
+        <v>208.1910289934046</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>0</v>
+        <v>184.8687752702672</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>0</v>
+        <v>164.3234773690706</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>0</v>
+        <v>144.8082939412932</v>
       </c>
       <c r="N3" s="8" t="n">
-        <v>0</v>
+        <v>126.2958676328881</v>
       </c>
     </row>
     <row r="4" ht="15.5" customHeight="1">
@@ -1613,41 +1627,41 @@
           <t>M$</t>
         </is>
       </c>
-      <c r="C5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="8" t="n">
-        <v>0</v>
+      <c r="C5" s="14" t="n">
+        <v>3.70615745010529</v>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>6.821846022778045</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>6.791494106384868</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>6.761445709155623</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>6.731697795898672</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>6.702247361774289</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>5.160453560085877</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>3.62926828258532</v>
+      </c>
+      <c r="K5" s="14" t="n">
+        <v>3.614333828012156</v>
+      </c>
+      <c r="L5" s="14" t="n">
+        <v>3.599548717984723</v>
+      </c>
+      <c r="M5" s="14" t="n">
+        <v>3.584911459057564</v>
+      </c>
+      <c r="N5" s="14" t="n">
+        <v>3.491718583690385</v>
       </c>
     </row>
     <row r="6" ht="15.5" customHeight="1">
@@ -1710,40 +1724,40 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>0</v>
+        <v>25.44686120688618</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>0</v>
+        <v>42.10740953541359</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>0</v>
+        <v>64.57807895901954</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>0</v>
+        <v>86.95886321779967</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>0</v>
+        <v>109.2511148262371</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>0</v>
+        <v>131.4561682370415</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0</v>
+        <v>153.5753400671338</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>0</v>
+        <v>157.4674299983288</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>0</v>
+        <v>159.7189237155807</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>0</v>
+        <v>161.9650122033525</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>0</v>
+        <v>164.2057917559879</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>0</v>
+        <v>166.441357282467</v>
       </c>
     </row>
     <row r="8" ht="15.5" customHeight="1">
@@ -1758,7 +1772,7 @@
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>0</v>
@@ -1797,429 +1811,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20.81640625" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>Inputs</t>
-        </is>
-      </c>
-      <c r="B1" s="13" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D1" s="4" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E1" s="4" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F1" s="4" t="n">
-        <v>2026</v>
-      </c>
-      <c r="G1" s="4" t="n">
-        <v>2027</v>
-      </c>
-      <c r="H1" s="4" t="n">
-        <v>2028</v>
-      </c>
-      <c r="I1" s="4" t="n">
-        <v>2029</v>
-      </c>
-      <c r="J1" s="4" t="n">
-        <v>2030</v>
-      </c>
-      <c r="K1" s="4" t="n">
-        <v>2031</v>
-      </c>
-      <c r="L1" s="4" t="n">
-        <v>2032</v>
-      </c>
-      <c r="M1" s="4" t="n">
-        <v>2033</v>
-      </c>
-      <c r="N1" s="4" t="n">
-        <v>2034</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>Tariff</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>$/kWh</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>Demand</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>kWh</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Outputs</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CAPEX - Growth</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>M$</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CAPEX - Maintenance</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>M$</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>OPEX</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>M$</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>D&amp;A</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/backend/Rwanda/technoeconomic-inputs-Aligned.xlsx
+++ b/backend/Rwanda/technoeconomic-inputs-Aligned.xlsx
@@ -266,6 +266,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/backend/Rwanda/technoeconomic-inputs-Aligned.xlsx
+++ b/backend/Rwanda/technoeconomic-inputs-Aligned.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/Rwanda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{B32ABF18-016C-4A2F-8E13-31B8053C754B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B42B1DE-C00B-4DE6-9F77-B2D31BED82B0}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{B32ABF18-016C-4A2F-8E13-31B8053C754B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE709E85-FB23-4E62-B532-684C442AFCCF}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -67,13 +67,13 @@
     <t>years</t>
   </si>
   <si>
-    <t>Type - Inputs</t>
-  </si>
-  <si>
     <t>GRID</t>
   </si>
   <si>
     <t>OFF-GRID</t>
+  </si>
+  <si>
+    <t>System</t>
   </si>
 </sst>
 </file>
@@ -248,6 +248,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -800,7 +804,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>0</v>
@@ -847,7 +851,7 @@
     </row>
     <row r="2" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" s="13" t="s">
         <v>2</v>
@@ -894,7 +898,7 @@
     </row>
     <row r="3" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="16" t="s">
         <v>4</v>
@@ -941,7 +945,7 @@
     </row>
     <row r="4" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>6</v>
@@ -988,7 +992,7 @@
     </row>
     <row r="5" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="17" t="s">
         <v>7</v>
@@ -1035,7 +1039,7 @@
     </row>
     <row r="6" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" s="17" t="s">
         <v>8</v>
@@ -1082,7 +1086,7 @@
     </row>
     <row r="7" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>2</v>
@@ -1129,7 +1133,7 @@
     </row>
     <row r="8" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>4</v>
@@ -1176,7 +1180,7 @@
     </row>
     <row r="9" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" s="16" t="s">
         <v>6</v>
@@ -1223,7 +1227,7 @@
     </row>
     <row r="10" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" s="17" t="s">
         <v>7</v>
@@ -1270,7 +1274,7 @@
     </row>
     <row r="11" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" s="17" t="s">
         <v>8</v>
@@ -1331,7 +1335,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>0</v>
@@ -1378,7 +1382,7 @@
     </row>
     <row r="2" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" s="13" t="s">
         <v>2</v>
@@ -1425,7 +1429,7 @@
     </row>
     <row r="3" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="16" t="s">
         <v>4</v>
@@ -1472,7 +1476,7 @@
     </row>
     <row r="4" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>6</v>
@@ -1519,7 +1523,7 @@
     </row>
     <row r="5" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="17" t="s">
         <v>7</v>
@@ -1566,7 +1570,7 @@
     </row>
     <row r="6" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" s="17" t="s">
         <v>8</v>
@@ -1613,7 +1617,7 @@
     </row>
     <row r="7" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>2</v>
@@ -1660,7 +1664,7 @@
     </row>
     <row r="8" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>4</v>
@@ -1707,7 +1711,7 @@
     </row>
     <row r="9" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" s="16" t="s">
         <v>6</v>
@@ -1754,7 +1758,7 @@
     </row>
     <row r="10" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" s="17" t="s">
         <v>7</v>
@@ -1801,7 +1805,7 @@
     </row>
     <row r="11" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" s="17" t="s">
         <v>8</v>

--- a/backend/Rwanda/technoeconomic-inputs-Aligned.xlsx
+++ b/backend/Rwanda/technoeconomic-inputs-Aligned.xlsx
@@ -7,8 +7,8 @@
   </bookViews>
   <sheets>
     <sheet name="LPG" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Electricity (Low access)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Electricity &amp; E-Cooking" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Electricity &amp; E-Cooking" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Electricity (Low access)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterate="1"/>
@@ -819,14 +819,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <dimension ref="A1:O11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.54296875" customWidth="1" min="1" max="1"/>
     <col width="25.453125" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.65" customHeight="1">
+    <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
           <t>System</t>
@@ -879,7 +879,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="2" ht="15.65" customHeight="1">
+    <row r="2">
       <c r="A2" s="13" t="inlineStr">
         <is>
           <t>GRID</t>
@@ -896,43 +896,43 @@
         </is>
       </c>
       <c r="D2" s="15" t="n">
-        <v>1442.594335096599</v>
+        <v>1473.57</v>
       </c>
       <c r="E2" s="15" t="n">
-        <v>1504.709837541243</v>
+        <v>1578.81</v>
       </c>
       <c r="F2" s="15" t="n">
-        <v>1599.368341608153</v>
+        <v>1718.68</v>
       </c>
       <c r="G2" s="15" t="n">
-        <v>1686.171912334703</v>
+        <v>1846.2</v>
       </c>
       <c r="H2" s="15" t="n">
-        <v>1765.425157458315</v>
+        <v>1962.03</v>
       </c>
       <c r="I2" s="15" t="n">
-        <v>1837.444117677565</v>
+        <v>2066.78</v>
       </c>
       <c r="J2" s="15" t="n">
-        <v>1902.551376848396</v>
+        <v>2161.04</v>
       </c>
       <c r="K2" s="15" t="n">
-        <v>1964.327964492503</v>
+        <v>2284.73</v>
       </c>
       <c r="L2" s="15" t="n">
-        <v>2022.785398360768</v>
+        <v>2397.74</v>
       </c>
       <c r="M2" s="15" t="n">
-        <v>2075.479228997338</v>
+        <v>2499.08</v>
       </c>
       <c r="N2" s="15" t="n">
-        <v>2122.631550311323</v>
+        <v>2877.08</v>
       </c>
       <c r="O2" s="15" t="n">
-        <v>2164.450166783826</v>
-      </c>
-    </row>
-    <row r="3" ht="15.65" customHeight="1">
+        <v>2669.27</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="16" t="inlineStr">
         <is>
           <t>GRID</t>
@@ -949,43 +949,43 @@
         </is>
       </c>
       <c r="D3" s="15" t="n">
-        <v>214.8070553210895</v>
+        <v>242.2</v>
       </c>
       <c r="E3" s="15" t="n">
-        <v>248.020871355366</v>
+        <v>294.74</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>245.5406626418123</v>
+        <v>291.79</v>
       </c>
       <c r="G3" s="15" t="n">
-        <v>243.0852560153942</v>
+        <v>288.87</v>
       </c>
       <c r="H3" s="15" t="n">
-        <v>240.6544034552403</v>
+        <v>285.98</v>
       </c>
       <c r="I3" s="15" t="n">
-        <v>238.2478594206879</v>
+        <v>283.12</v>
       </c>
       <c r="J3" s="15" t="n">
-        <v>273.9304205498366</v>
+        <v>340.66</v>
       </c>
       <c r="K3" s="15" t="n">
-        <v>309.0653526620416</v>
+        <v>397.32</v>
       </c>
       <c r="L3" s="15" t="n">
-        <v>305.9746991354211</v>
+        <v>393.35</v>
       </c>
       <c r="M3" s="15" t="n">
-        <v>302.914952144067</v>
+        <v>389.41</v>
       </c>
       <c r="N3" s="15" t="n">
-        <v>299.8858026226263</v>
+        <v>385.52</v>
       </c>
       <c r="O3" s="15" t="n">
-        <v>206.371686125674</v>
-      </c>
-    </row>
-    <row r="4" ht="15.65" customHeight="1">
+        <v>259.22</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
           <t>GRID</t>
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="D4" s="15" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="15" t="n">
         <v>0</v>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" ht="15.65" customHeight="1">
+    <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
           <t>GRID</t>
@@ -1055,43 +1055,43 @@
         </is>
       </c>
       <c r="D5" s="15" t="n">
-        <v>46.18373564251058</v>
+        <v>48.2</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>49.26293246654923</v>
+        <v>53.31</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>53.45734619153793</v>
+        <v>59.62</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>57.56294534878022</v>
+        <v>65.8</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>61.5810867882585</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="I5" s="15" t="n">
-        <v>65.51310910441234</v>
+        <v>77.78</v>
       </c>
       <c r="J5" s="15" t="n">
-        <v>69.36033286556427</v>
+        <v>83.58</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>77.45575053899586</v>
+        <v>92.56999999999999</v>
       </c>
       <c r="L5" s="15" t="n">
-        <v>86.42268175129648</v>
+        <v>101.42</v>
       </c>
       <c r="M5" s="15" t="n">
-        <v>95.2025287642972</v>
+        <v>110.08</v>
       </c>
       <c r="N5" s="15" t="n">
-        <v>103.7981365688628</v>
+        <v>118.55</v>
       </c>
       <c r="O5" s="15" t="n">
-        <v>112.2123119644606</v>
-      </c>
-    </row>
-    <row r="6" ht="15.65" customHeight="1">
+        <v>126.84</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="16" t="inlineStr">
         <is>
           <t>GRID</t>
@@ -1110,41 +1110,63 @@
       <c r="D6" s="15" t="n">
         <v>35</v>
       </c>
-      <c r="E6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="15.65" customHeight="1">
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J6" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M6" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O6" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
           <t>OFF-GRID</t>
@@ -1164,40 +1186,40 @@
         <v>368.39</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>370.3375301687133</v>
+        <v>370.34</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>377.2737822950851</v>
+        <v>377.27</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>378.1374686057446</v>
+        <v>378.14</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>373.7200362575149</v>
+        <v>373.72</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>364.7286948963981</v>
+        <v>364.73</v>
       </c>
       <c r="J7" s="15" t="n">
-        <v>351.7957548427549</v>
+        <v>351.8</v>
       </c>
       <c r="K7" s="15" t="n">
-        <v>341.393316081468</v>
+        <v>341.39</v>
       </c>
       <c r="L7" s="15" t="n">
-        <v>326.9645235724591</v>
+        <v>326.96</v>
       </c>
       <c r="M7" s="15" t="n">
-        <v>308.8777374296963</v>
+        <v>308.88</v>
       </c>
       <c r="N7" s="15" t="n">
-        <v>287.7083204946137</v>
+        <v>287.71</v>
       </c>
       <c r="O7" s="15" t="n">
-        <v>263.9913409399228</v>
-      </c>
-    </row>
-    <row r="8" ht="15.65" customHeight="1">
+        <v>263.99</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="16" t="inlineStr">
         <is>
           <t>OFF-GRID</t>
@@ -1214,43 +1236,43 @@
         </is>
       </c>
       <c r="D8" s="15" t="n">
-        <v>39.20533020612309</v>
+        <v>39.21</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>49.66803257508351</v>
+        <v>49.67</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>49.17135224933267</v>
+        <v>49.17</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>48.67963872683934</v>
+        <v>48.68</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>48.19284233957096</v>
+        <v>48.19</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>47.71091391617525</v>
+        <v>47.71</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>17.3764528627935</v>
+        <v>17.38</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>-12.50500172575464</v>
+        <v>-12.51</v>
       </c>
       <c r="L8" s="15" t="n">
-        <v>-12.37995170849709</v>
+        <v>-12.38</v>
       </c>
       <c r="M8" s="15" t="n">
-        <v>-12.25615219141212</v>
+        <v>-12.26</v>
       </c>
       <c r="N8" s="15" t="n">
-        <v>-12.133590669498</v>
+        <v>-12.13</v>
       </c>
       <c r="O8" s="15" t="n">
-        <v>0.9231042276977806</v>
-      </c>
-    </row>
-    <row r="9" ht="15.65" customHeight="1">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" s="16" t="inlineStr">
         <is>
           <t>OFF-GRID</t>
@@ -1303,7 +1325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" ht="15.65" customHeight="1">
+    <row r="10">
       <c r="A10" s="16" t="inlineStr">
         <is>
           <t>OFF-GRID</t>
@@ -1320,43 +1342,43 @@
         </is>
       </c>
       <c r="D10" s="15" t="n">
-        <v>56.13416700255231</v>
+        <v>56.13</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>63.13219928987156</v>
+        <v>63.13</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>71.77450880827612</v>
+        <v>71.77</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>80.23765891638362</v>
+        <v>80.23999999999999</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>88.52436857144815</v>
+        <v>88.52</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>96.63732026751975</v>
+        <v>96.64</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>104.5791604928127</v>
+        <v>104.58</v>
       </c>
       <c r="K10" s="15" t="n">
-        <v>103.3411052008041</v>
+        <v>103.34</v>
       </c>
       <c r="L10" s="15" t="n">
-        <v>98.26081872793341</v>
+        <v>98.26000000000001</v>
       </c>
       <c r="M10" s="15" t="n">
-        <v>93.27180387400006</v>
+        <v>93.27</v>
       </c>
       <c r="N10" s="15" t="n">
-        <v>88.37274323527257</v>
+        <v>88.37</v>
       </c>
       <c r="O10" s="15" t="n">
-        <v>83.56233662893223</v>
-      </c>
-    </row>
-    <row r="11" ht="15.65" customHeight="1">
+        <v>83.56</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
           <t>OFF-GRID</t>
@@ -1375,53 +1397,61 @@
       <c r="D11" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="E11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="D19" s="18" t="n"/>
-      <c r="E19" s="18" t="n"/>
-      <c r="F19" s="18" t="n"/>
-      <c r="G19" s="18" t="n"/>
-      <c r="H19" s="18" t="n"/>
-      <c r="I19" s="18" t="n"/>
-      <c r="J19" s="18" t="n"/>
-      <c r="K19" s="18" t="n"/>
-      <c r="L19" s="18" t="n"/>
-      <c r="M19" s="18" t="n"/>
-      <c r="N19" s="18" t="n"/>
-      <c r="O19" s="18" t="n"/>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J11" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L11" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M11" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O11" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1511,40 +1541,40 @@
         </is>
       </c>
       <c r="D2" s="15" t="n">
-        <v>1473.57</v>
+        <v>1442.59</v>
       </c>
       <c r="E2" s="15" t="n">
-        <v>1578.81</v>
+        <v>1504.71</v>
       </c>
       <c r="F2" s="15" t="n">
-        <v>1718.68</v>
+        <v>1599.37</v>
       </c>
       <c r="G2" s="15" t="n">
-        <v>1846.2</v>
+        <v>1686.17</v>
       </c>
       <c r="H2" s="15" t="n">
-        <v>1962.03</v>
+        <v>1765.43</v>
       </c>
       <c r="I2" s="15" t="n">
-        <v>2066.78</v>
+        <v>1837.44</v>
       </c>
       <c r="J2" s="15" t="n">
-        <v>2161.04</v>
+        <v>1902.55</v>
       </c>
       <c r="K2" s="15" t="n">
-        <v>2284.73</v>
+        <v>1964.33</v>
       </c>
       <c r="L2" s="15" t="n">
-        <v>2397.74</v>
+        <v>2022.79</v>
       </c>
       <c r="M2" s="15" t="n">
-        <v>2499.08</v>
+        <v>2075.48</v>
       </c>
       <c r="N2" s="15" t="n">
-        <v>2877.08</v>
+        <v>2122.63</v>
       </c>
       <c r="O2" s="15" t="n">
-        <v>2669.27</v>
+        <v>2164.45</v>
       </c>
     </row>
     <row r="3">
@@ -1564,40 +1594,40 @@
         </is>
       </c>
       <c r="D3" s="15" t="n">
-        <v>242.2</v>
+        <v>214.81</v>
       </c>
       <c r="E3" s="15" t="n">
-        <v>294.74</v>
+        <v>248.02</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>291.79</v>
+        <v>245.54</v>
       </c>
       <c r="G3" s="15" t="n">
-        <v>288.87</v>
+        <v>243.09</v>
       </c>
       <c r="H3" s="15" t="n">
-        <v>285.98</v>
+        <v>240.65</v>
       </c>
       <c r="I3" s="15" t="n">
-        <v>283.12</v>
+        <v>238.25</v>
       </c>
       <c r="J3" s="15" t="n">
-        <v>340.66</v>
+        <v>273.93</v>
       </c>
       <c r="K3" s="15" t="n">
-        <v>397.32</v>
+        <v>309.07</v>
       </c>
       <c r="L3" s="15" t="n">
-        <v>393.35</v>
+        <v>305.97</v>
       </c>
       <c r="M3" s="15" t="n">
-        <v>389.41</v>
+        <v>302.91</v>
       </c>
       <c r="N3" s="15" t="n">
-        <v>385.52</v>
+        <v>299.89</v>
       </c>
       <c r="O3" s="15" t="n">
-        <v>259.22</v>
+        <v>206.37</v>
       </c>
     </row>
     <row r="4">
@@ -1670,40 +1700,40 @@
         </is>
       </c>
       <c r="D5" s="15" t="n">
-        <v>48.2</v>
+        <v>46.18</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>53.31</v>
+        <v>49.26</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>59.62</v>
+        <v>53.46</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>65.8</v>
+        <v>57.56</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>71.84999999999999</v>
+        <v>61.58</v>
       </c>
       <c r="I5" s="15" t="n">
-        <v>77.78</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="J5" s="15" t="n">
-        <v>83.58</v>
+        <v>69.36</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>92.56999999999999</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="L5" s="15" t="n">
-        <v>101.42</v>
+        <v>86.42</v>
       </c>
       <c r="M5" s="15" t="n">
-        <v>110.08</v>
+        <v>95.2</v>
       </c>
       <c r="N5" s="15" t="n">
-        <v>118.55</v>
+        <v>103.8</v>
       </c>
       <c r="O5" s="15" t="n">
-        <v>126.84</v>
+        <v>112.21</v>
       </c>
     </row>
     <row r="6">
